--- a/test_cases/test_data.xlsx
+++ b/test_cases/test_data.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_project\ui_selenium_by_keyword\test_cases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28117" windowHeight="12480"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="45">
   <si>
     <t>说明</t>
   </si>
@@ -55,72 +74,75 @@
     <t>allure_feature</t>
   </si>
   <si>
+    <t>CMS</t>
+  </si>
+  <si>
+    <t>allure_story</t>
+  </si>
+  <si>
+    <t>登录</t>
+  </si>
+  <si>
+    <t>allure_title</t>
+  </si>
+  <si>
+    <t>打开访问页面</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>https://gameetcms.chuntiangl.com/</t>
+  </si>
+  <si>
+    <t>输入用户名</t>
+  </si>
+  <si>
+    <t>input_text</t>
+  </si>
+  <si>
+    <t>${user_name_input}</t>
+  </si>
+  <si>
+    <t>${get_username()}</t>
+  </si>
+  <si>
+    <t>输入密码</t>
+  </si>
+  <si>
+    <t>${password_input}</t>
+  </si>
+  <si>
+    <t>${get_password()}</t>
+  </si>
+  <si>
+    <t>点击登录按钮</t>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
+    <t>${login_btn}</t>
+  </si>
+  <si>
+    <t>断言文本</t>
+  </si>
+  <si>
+    <t>assert_equal</t>
+  </si>
+  <si>
+    <t>${login_success}</t>
+  </si>
+  <si>
+    <t>首页</t>
+  </si>
+  <si>
+    <t>异常登录</t>
+  </si>
+  <si>
     <t>运营端</t>
   </si>
   <si>
-    <t>allure_story</t>
-  </si>
-  <si>
-    <t>登录</t>
-  </si>
-  <si>
-    <t>allure_title</t>
-  </si>
-  <si>
-    <t>打开访问页面</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>http://121.37.190.62:9200/login</t>
-  </si>
-  <si>
-    <t>输入用户名</t>
-  </si>
-  <si>
-    <t>input_text</t>
-  </si>
-  <si>
-    <t>${user_name_input}</t>
-  </si>
-  <si>
-    <t>${get_username()}</t>
-  </si>
-  <si>
-    <t>输入密码</t>
-  </si>
-  <si>
-    <t>${password_input}</t>
-  </si>
-  <si>
-    <t>${get_password()}</t>
-  </si>
-  <si>
-    <t>点击登录按钮</t>
-  </si>
-  <si>
-    <t>click</t>
-  </si>
-  <si>
-    <t>${login_btn}</t>
-  </si>
-  <si>
-    <t>断言文本</t>
-  </si>
-  <si>
-    <t>assert_equal</t>
-  </si>
-  <si>
-    <t>${login_success_text}</t>
-  </si>
-  <si>
-    <t>登录成功</t>
-  </si>
-  <si>
-    <t>异常登录</t>
-  </si>
-  <si>
     <t>密码错误常登录</t>
   </si>
   <si>
@@ -128,19 +150,37 @@
   </si>
   <si>
     <t>onesports1</t>
+  </si>
+  <si>
+    <t>${login_error}</t>
+  </si>
+  <si>
+    <t>请求错误 : fail</t>
+  </si>
+  <si>
+    <t>查看充值订单</t>
+  </si>
+  <si>
+    <t>auto_login_admin</t>
+  </si>
+  <si>
+    <t>点击订单管理菜单</t>
+  </si>
+  <si>
+    <t>//*[@id="root"]/div[1]/section/aside/div/div[1]/ul/li[3]/div/span/span/span[2]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,19 +196,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <sz val="9.8"/>
+      <color rgb="FF56A8F5"/>
+      <name val="Courier New"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9.8"/>
@@ -179,6 +210,20 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -186,30 +231,41 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -222,41 +278,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -307,7 +331,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,49 +373,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -382,121 +511,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,21 +599,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -597,6 +627,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,148 +700,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -816,71 +861,71 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="10" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -977,7 +1022,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="绿色中色系渐变风标题行镶边行表格样式" count="4">
+    <tableStyle name="绿色中色系渐变风标题行镶边行表格样式" count="4" xr9:uid="{86E05CB8-13E6-456A-B988-2248DE322E8E}">
       <tableStyleElement type="wholeTable" dxfId="3"/>
       <tableStyleElement type="headerRow" dxfId="2"/>
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
@@ -994,7 +1039,20 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="表3" displayName="表3" ref="A1:D21" totalsRowShown="0">
-  <autoFilter ref="A1:D21"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D21" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="说明"/>
+    <tableColumn id="2" name="标记"/>
+    <tableColumn id="3" name="列1"/>
+    <tableColumn id="4" name="列2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表3_3" displayName="表3_3" ref="A1:D7" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D7" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="4">
     <tableColumn id="1" name="说明"/>
     <tableColumn id="2" name="标记"/>
@@ -1264,12 +1322,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.02777777777778" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="27.1592920353982" customWidth="1"/>
-    <col min="2" max="2" width="21.0442477876106" customWidth="1"/>
-    <col min="3" max="3" width="61.4690265486726" customWidth="1"/>
-    <col min="4" max="4" width="42.283185840708" customWidth="1"/>
+    <col min="1" max="1" width="27.1574074074074" customWidth="1"/>
+    <col min="2" max="2" width="21.0462962962963" customWidth="1"/>
+    <col min="3" max="3" width="61.4722222222222" customWidth="1"/>
+    <col min="4" max="4" width="42.287037037037" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:4">
@@ -1316,37 +1374,37 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
@@ -1355,7 +1413,7 @@
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="2"/>
@@ -1392,7 +1450,7 @@
       <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -1444,11 +1502,11 @@
       <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>13</v>
+      <c r="C14" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D14" s="9"/>
     </row>
@@ -1456,10 +1514,10 @@
       <c r="A15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="9"/>
@@ -1468,11 +1526,11 @@
       <c r="A16" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>35</v>
+      <c r="C16" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D16" s="9"/>
     </row>
@@ -1483,7 +1541,7 @@
       <c r="B17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D17" s="4"/>
@@ -1499,7 +1557,7 @@
         <v>22</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1513,7 +1571,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1536,17 +1594,122 @@
         <v>31</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C17" r:id="rId2" display="http://121.37.190.62:9200/login" tooltip="http://121.37.190.62:9200/login"/>
-    <hyperlink ref="C7" r:id="rId2" display="http://121.37.190.62:9200/login" tooltip="http://121.37.190.62:9200/login"/>
-  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9.02777777777778" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="27.1574074074074" customWidth="1"/>
+    <col min="2" max="2" width="21.0462962962963" customWidth="1"/>
+    <col min="3" max="3" width="61.4722222222222" customWidth="1"/>
+    <col min="4" max="4" width="42.287037037037" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <tableParts count="1">
